--- a/out_demo/report_2024.xlsx
+++ b/out_demo/report_2024.xlsx
@@ -20,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -66,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -78,6 +80,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -506,7 +509,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IVAFE (RW)</t>
+          <t>IVAFE (RW) teorica</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -514,48 +517,58 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>TOTALE IMPOSTE DOVUTE</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>1154.05</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IVAFE da versare</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Minusvalenza dell'anno da riportare</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>0</v>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>TOTALE IMPOSTE DA VERSARE</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1088.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ritenute estere subite (info)</t>
+          <t>Minusvalenza dell'anno da riportare</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>14.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Credito teorico rimborso (info)</t>
+          <t>Ritenute estere subite (info)</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>14.17</v>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Credito teorico rimborso (info)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>14.17</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>AVVISO: questo prospetto è prodotto da uno strumento automatico di supporto al calcolo e NON sostituisce la consulenza di un commercialista. Diversi trattamenti fiscali sono normativamente incerti (frontiera dividendi, IVAFE su CFD/OTC, dividend adjustment, PIL). Verificare tutti i valori e i casi segnalati nei warning con un professionista prima di presentare la dichiarazione dei redditi.</t>
         </is>
@@ -721,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -729,13 +742,15 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -751,50 +766,60 @@
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
+          <t>Stato AdE</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Alq.</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
           <t>Pay date</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Lordo ccy</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Ritenuta ccy</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Lordo €</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Ritenuta €</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Base imp. €</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Imposta €</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Credito teor. €</t>
         </is>
@@ -813,36 +838,44 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>069</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>1.0583</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>94.48999999999999</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>14.17</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>94.48999999999999</v>
       </c>
       <c r="K2" s="2" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>94.48999999999999</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>24.57</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>14.17</v>
       </c>
     </row>
@@ -951,21 +984,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -986,45 +1020,50 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
+          <t>Stato AdE</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
           <t>Cod. valoriz.</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Valore iniz. €</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Valore fin. €</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Giorni</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Quota %</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>IVAFE applic.</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Aliquota</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>IVAFE €</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Solo monit.</t>
         </is>
@@ -1048,33 +1087,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>040</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="F2" s="2" t="n">
         <v>16506</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>158</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>100</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Sì</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.002</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1094,33 +1138,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>040</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>13755</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>17654</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>352</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>100</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Sì</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.002</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>34.05</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1140,33 +1189,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
+          <t>040</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>9170</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>6694</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>365</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>100</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Sì</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.002</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>13.39</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5"/>
     <row r="6">
@@ -1175,11 +1229,18 @@
           <t>TOTALE</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>24348</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>65.14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>IVAFE 65.14 € ≤ 200 €: VERSAMENTO NON DOVUTO (solo obbligo dichiarativo RW) [art. 19 c.20 DL 201/2011]</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1231,7 +1292,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Dividendi tassati al LORDO frontiera (posizione AdE). Ritenute estere per € 14.17 non scomputate: credito teorico € 14.17 recuperabile solo con istanza di rimborso (esito incerto).</t>
+          <t>Dividendi tassati al LORDO frontiera (posizione AdE). Ritenute estere per € 14.17 non scomputate: credito teorico € 14.17 recuperabile solo con istanza di rimborso (esito incerto; Cass. 25698/2022 e 10204/2024 sono favorevoli ma la prassi AdE resta contraria — interpello 111/2020).</t>
         </is>
       </c>
     </row>
